--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-YNT-MTR-02_fabrika_risk_analizi_ana_guvence_plani__risk_haritasi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/02_CMP2 - Risk, İş Sürekliliği ve Bilgi Sistemleri/EKG-YNT-MTR-02_fabrika_risk_analizi_ana_guvence_plani__risk_haritasi.xlsx
@@ -1304,7 +1304,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Fabrika Risk Analizi (Ana Güvence Planı / risk haritası)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Risk puan formülleri eksik, aralık dışı ve kesirli girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R686c36e542964b45"/>
   <x:tableParts count="1">
@@ -1957,7 +1958,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Fabrika Risk Analizi (Ana Güvence Planı / risk haritası)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Risk puan formülleri eksik, aralık dışı ve kesirli girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63cca2b9164844f4"/>
   <x:tableParts count="1">
@@ -2531,7 +2533,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-MTR-02&amp;C&amp;"Arial,Regular"&amp;11Fabrika Risk Analizi (Ana Güvence Planı / risk haritası)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 01.09.2026
+Revizyon nedeni: Risk puan formülleri eksik, aralık dışı ve kesirli girdide sonuç üretmeyecek şekilde düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13a4d472efc44800"/>
   <x:tableParts count="1">
